--- a/src/tests/data/output/tuc_17_1_ieee14_cim_converter.xlsx
+++ b/src/tests/data/output/tuc_17_1_ieee14_cim_converter.xlsx
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>14:59:35</t>
+          <t>15:22:19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -511,7 +511,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>14:59:35</t>
+          <t>15:22:19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -549,7 +549,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>14:59:35</t>
+          <t>15:22:19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>14:59:35</t>
+          <t>15:22:19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -625,7 +625,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>14:59:35</t>
+          <t>15:22:19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -663,7 +663,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>14:59:35</t>
+          <t>15:22:19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -701,7 +701,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>14:59:35</t>
+          <t>15:22:19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>14:59:35</t>
+          <t>15:22:19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -777,7 +777,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>14:59:35</t>
+          <t>15:22:19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>14:59:35</t>
+          <t>15:22:19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
